--- a/catalog/kober/precios_renovai_plantilla.xlsx
+++ b/catalog/kober/precios_renovai_plantilla.xlsx
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -718,41 +718,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cuota_visita_SELF</t>
+          <t>cuota_visita</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cuota de la visita de medición, el cliente instala</t>
+          <t>visita de medición: sin costo si el cliente contrata la obra; si no, se cobra esta cuota (más IVA)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cuota_visita_MANAGED</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>500</v>
-      </c>
+          <t>responsable</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
-        <is>
-          <t>cuota de la visita, instalamos nosotros</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>responsable</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
         <is>
           <t>quién mantiene estos precios</t>
         </is>
